--- a/BWI/bestwine_output/bestwine_Botswana.xlsx
+++ b/BWI/bestwine_output/bestwine_Botswana.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA11"/>
+  <dimension ref="A1:AA12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1697,6 +1697,103 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Lengau</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Lengau</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>40353</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Gaborone</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Gaborone</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Plot 10221 Maporoporo Rd Broadhurst Industrial Prk</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lengau.co.bw</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@lengau.co.bw</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>+267 395 2639</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LengauWineCompany/</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Violet Sabakaki</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/violet-sabakaki-680bb094/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Botswana.xlsx
+++ b/BWI/bestwine_output/bestwine_Botswana.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA12"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1794,6 +1794,103 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Lengau</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Lengau</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>40353</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Gaborone</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Gaborone</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>Plot 10221 Maporoporo Rd Broadhurst Industrial Prk</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lengau.co.bw</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@lengau.co.bw</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>+267 395 2639</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LengauWineCompany/</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>Violet Sabakaki</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/violet-sabakaki-680bb094/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Botswana.xlsx
+++ b/BWI/bestwine_output/bestwine_Botswana.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA13"/>
+  <dimension ref="A1:AA14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1891,6 +1891,103 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Lengau</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Lengau</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>40353</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Gaborone</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Gaborone</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Plot 10221 Maporoporo Rd Broadhurst Industrial Prk</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lengau.co.bw</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@lengau.co.bw</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>+267 395 2639</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LengauWineCompany/</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>Violet Sabakaki</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/violet-sabakaki-680bb094/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Botswana.xlsx
+++ b/BWI/bestwine_output/bestwine_Botswana.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA14"/>
+  <dimension ref="A1:AA15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1988,6 +1988,103 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Lengau</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Lengau</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>40353</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Botswana</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Gaborone</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Gaborone</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Plot 10221 Maporoporo Rd Broadhurst Industrial Prk</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lengau.co.bw</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>enquiries@lengau.co.bw</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>+267 395 2639</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LengauWineCompany/</t>
+        </is>
+      </c>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr"/>
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>Violet Sabakaki</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/violet-sabakaki-680bb094/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
